--- a/artfynd/A 30985-2022 artfynd.xlsx
+++ b/artfynd/A 30985-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155215</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155217</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155228</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155232</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155237</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155254</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155274</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155276</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155277</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155279</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1904,6 +1959,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155338</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155340</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155341</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155342</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2352,6 +2427,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155345</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2464,6 +2544,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155348</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155350</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2688,6 +2778,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155351</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2800,6 +2895,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155354</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155355</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3024,6 +3129,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155357</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3136,6 +3246,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155543</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3248,6 +3363,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155544</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3360,6 +3480,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155557</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3472,6 +3597,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155558</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3584,6 +3714,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155564</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3696,6 +3831,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155565</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3808,6 +3948,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155566</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3920,6 +4065,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155568</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4032,6 +4182,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155572</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4144,6 +4299,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155574</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4256,6 +4416,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155575</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4368,6 +4533,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155576</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4480,6 +4650,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155577</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4592,6 +4767,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155578</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4704,6 +4884,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155581</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4816,6 +5001,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155582</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4928,6 +5118,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155583</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5040,6 +5235,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155584</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5152,6 +5352,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155586</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5264,6 +5469,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155592</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5376,6 +5586,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155593</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5488,6 +5703,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155594</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5600,6 +5820,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155595</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5712,6 +5937,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155605</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5824,6 +6054,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155606</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5936,6 +6171,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155607</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6048,6 +6288,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155608</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6160,6 +6405,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155610</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6272,6 +6522,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155613</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6384,6 +6639,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155614</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6496,6 +6756,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155615</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6608,6 +6873,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155618</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6720,6 +6990,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155619</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6832,6 +7107,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155620</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6944,6 +7224,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155633</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7056,6 +7341,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155635</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7168,6 +7458,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155636</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7280,6 +7575,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155637</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7392,6 +7692,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155638</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7504,6 +7809,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155639</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7616,6 +7926,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155640</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7728,6 +8043,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155641</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7840,6 +8160,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155642</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7952,6 +8277,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155643</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8064,6 +8394,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155644</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8176,6 +8511,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155645</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8288,6 +8628,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155647</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8400,6 +8745,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155648</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8512,6 +8862,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155652</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8624,6 +8979,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155653</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8736,6 +9096,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155654</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8848,6 +9213,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155739</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8960,6 +9330,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155746</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9072,8 +9447,90 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>